--- a/datasets/Cleaned_data.xlsx
+++ b/datasets/Cleaned_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\leo\VCodeProjects\Analisis-Review\datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\leo\VCodeProjects\smartcard-systematic-mapping-review\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B190CA5C-88A9-43E1-AA24-11E4FC75E2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D3A6FE-9F70-4D42-A6C3-5979937EB251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4139" uniqueCount="1572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4139" uniqueCount="1596">
   <si>
     <t>Author Full Names</t>
   </si>
@@ -3403,9 +3403,6 @@
     <t>Analytical subcategory</t>
   </si>
   <si>
-    <t>Algorithm</t>
-  </si>
-  <si>
     <t>Algorithm type</t>
   </si>
   <si>
@@ -4642,9 +4639,6 @@
     <t>AVL, Fare and Schedule integration model;Dwell time model;Trip-chaining algorithm;Anomaly detection</t>
   </si>
   <si>
-    <t>Authors algorithm;Forecasting;Trip-chaining algorithm;Anomaly detection</t>
-  </si>
-  <si>
     <t>Trip-chaining algorithm</t>
   </si>
   <si>
@@ -4778,6 +4772,84 @@
   </si>
   <si>
     <t>P150</t>
+  </si>
+  <si>
+    <t>Methods</t>
+  </si>
+  <si>
+    <t>Techniques</t>
+  </si>
+  <si>
+    <t>Probability techniques;Probability techniques;Regression</t>
+  </si>
+  <si>
+    <t>Probability techniques</t>
+  </si>
+  <si>
+    <t>Clustering;Regression;Probability techniques</t>
+  </si>
+  <si>
+    <t>Regression;Probability techniques</t>
+  </si>
+  <si>
+    <t>Probability techniques;Regression</t>
+  </si>
+  <si>
+    <t>Authors technique;Clustering</t>
+  </si>
+  <si>
+    <t>Authors technique</t>
+  </si>
+  <si>
+    <t>Authors technique;Dimensionality reduction;Probability techniques</t>
+  </si>
+  <si>
+    <t>Regression;Authors technique</t>
+  </si>
+  <si>
+    <t>Authors technique;Regression</t>
+  </si>
+  <si>
+    <t>Authors technique;Forecasting;Trip-chaining algorithm;Anomaly detection</t>
+  </si>
+  <si>
+    <t>Neural networks;OD matrix;Authors technique</t>
+  </si>
+  <si>
+    <t>Authors technique;OD matrix</t>
+  </si>
+  <si>
+    <t>Classification;Authors technique</t>
+  </si>
+  <si>
+    <t>Authors technique;Graph model;Clustering</t>
+  </si>
+  <si>
+    <t>Deep learning;Authors technique</t>
+  </si>
+  <si>
+    <t>Economical model;Economical model;Economical model;Regression;Authors technique;Regression</t>
+  </si>
+  <si>
+    <t>Regression;Natural language processing;Clustering</t>
+  </si>
+  <si>
+    <t>Ranking algorithm;Regression;Natural language processing;Natural language processing</t>
+  </si>
+  <si>
+    <t>Natural language processing</t>
+  </si>
+  <si>
+    <t>Natural language processing;Descriptive statistics</t>
+  </si>
+  <si>
+    <t>Natural language processing;Classification</t>
+  </si>
+  <si>
+    <t>Natural language processing;Clustering;Clustering</t>
+  </si>
+  <si>
+    <t>Probability techniques;Natural language processing</t>
   </si>
 </sst>
 </file>
@@ -4989,7 +5061,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -5037,10 +5109,10 @@
         <v>1112</v>
       </c>
       <c r="U1" t="s">
-        <v>1113</v>
+        <v>1571</v>
       </c>
       <c r="V1" t="s">
-        <v>1114</v>
+        <v>1570</v>
       </c>
       <c r="W1" t="s">
         <v>14</v>
@@ -5127,7 +5199,7 @@
         <v>904</v>
       </c>
       <c r="V2" t="s">
-        <v>905</v>
+        <v>1595</v>
       </c>
       <c r="W2">
         <v>1</v>
@@ -5268,7 +5340,7 @@
         <v>401</v>
       </c>
       <c r="M4" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N4" t="s">
         <v>67</v>
@@ -5535,7 +5607,7 @@
         <v>1062</v>
       </c>
       <c r="U7" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="V7" t="s">
         <v>468</v>
@@ -5619,7 +5691,7 @@
         <v>1071</v>
       </c>
       <c r="U8" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="V8" t="s">
         <v>70</v>
@@ -5706,7 +5778,7 @@
         <v>86</v>
       </c>
       <c r="V9" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -6174,7 +6246,7 @@
         <v>1060</v>
       </c>
       <c r="U15" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="V15" t="s">
         <v>30</v>
@@ -6579,7 +6651,7 @@
         <v>716</v>
       </c>
       <c r="V20" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -6657,13 +6729,13 @@
         <v>44</v>
       </c>
       <c r="T21" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="U21" t="s">
         <v>424</v>
       </c>
       <c r="V21" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -6828,7 +6900,7 @@
         <v>771</v>
       </c>
       <c r="V23" t="s">
-        <v>772</v>
+        <v>1572</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -7143,7 +7215,7 @@
         <v>1077</v>
       </c>
       <c r="U27" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="V27" t="s">
         <v>720</v>
@@ -7224,7 +7296,7 @@
         <v>1060</v>
       </c>
       <c r="U28" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="V28" t="s">
         <v>373</v>
@@ -7308,7 +7380,7 @@
         <v>159</v>
       </c>
       <c r="V29" t="s">
-        <v>160</v>
+        <v>1589</v>
       </c>
       <c r="W29">
         <v>1</v>
@@ -7386,7 +7458,7 @@
         <v>1058</v>
       </c>
       <c r="U30" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="V30" t="s">
         <v>635</v>
@@ -7632,10 +7704,10 @@
         <v>1058</v>
       </c>
       <c r="U33" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="V33" t="s">
-        <v>184</v>
+        <v>1590</v>
       </c>
       <c r="W33">
         <v>0</v>
@@ -7872,7 +7944,7 @@
         <v>798</v>
       </c>
       <c r="V36" t="s">
-        <v>799</v>
+        <v>1579</v>
       </c>
       <c r="W36">
         <v>1</v>
@@ -7956,7 +8028,7 @@
         <v>781</v>
       </c>
       <c r="V37" t="s">
-        <v>451</v>
+        <v>1577</v>
       </c>
       <c r="W37">
         <v>0</v>
@@ -7971,7 +8043,7 @@
         <v>420</v>
       </c>
       <c r="AB37" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="AC37" t="s">
         <v>35</v>
@@ -8091,7 +8163,7 @@
         <v>730</v>
       </c>
       <c r="M39" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N39" t="s">
         <v>29</v>
@@ -8115,7 +8187,7 @@
         <v>617</v>
       </c>
       <c r="V39" t="s">
-        <v>618</v>
+        <v>1591</v>
       </c>
       <c r="W39">
         <v>0</v>
@@ -8280,7 +8352,7 @@
         <v>745</v>
       </c>
       <c r="V41" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -8616,7 +8688,7 @@
         <v>1074</v>
       </c>
       <c r="U45" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="V45" t="s">
         <v>486</v>
@@ -8691,10 +8763,10 @@
         <v>1076</v>
       </c>
       <c r="U46" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="V46" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -8763,10 +8835,10 @@
         <v>1062</v>
       </c>
       <c r="U47" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="V47" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="W47">
         <v>1</v>
@@ -8928,10 +9000,10 @@
         <v>1058</v>
       </c>
       <c r="U49" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="V49" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="W49">
         <v>0</v>
@@ -9012,7 +9084,7 @@
         <v>510</v>
       </c>
       <c r="V50" t="s">
-        <v>510</v>
+        <v>1573</v>
       </c>
       <c r="W50">
         <v>0</v>
@@ -9417,7 +9489,7 @@
         <v>1058</v>
       </c>
       <c r="U55" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="V55" t="s">
         <v>130</v>
@@ -9498,7 +9570,7 @@
         <v>1058</v>
       </c>
       <c r="U56" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="V56" t="s">
         <v>473</v>
@@ -9558,7 +9630,7 @@
         <v>735</v>
       </c>
       <c r="M57" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="N57" t="s">
         <v>158</v>
@@ -9579,7 +9651,7 @@
         <v>1058</v>
       </c>
       <c r="U57" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="V57" t="s">
         <v>736</v>
@@ -9663,7 +9735,7 @@
         <v>450</v>
       </c>
       <c r="V58" t="s">
-        <v>451</v>
+        <v>1577</v>
       </c>
       <c r="W58">
         <v>0</v>
@@ -9741,7 +9813,7 @@
         <v>1060</v>
       </c>
       <c r="U59" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="V59" t="s">
         <v>659</v>
@@ -9975,10 +10047,10 @@
         <v>1060</v>
       </c>
       <c r="U62" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="V62" t="s">
-        <v>211</v>
+        <v>1574</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -10296,7 +10368,7 @@
         <v>137</v>
       </c>
       <c r="V66" t="s">
-        <v>138</v>
+        <v>1592</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -10374,10 +10446,10 @@
         <v>1077</v>
       </c>
       <c r="U67" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="V67" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="W67">
         <v>0</v>
@@ -10449,7 +10521,7 @@
         <v>1066</v>
       </c>
       <c r="U68" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="V68" t="s">
         <v>176</v>
@@ -10623,7 +10695,7 @@
         <v>45</v>
       </c>
       <c r="V70" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -11112,7 +11184,7 @@
         <v>393</v>
       </c>
       <c r="U76" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="V76" t="s">
         <v>668</v>
@@ -11196,10 +11268,10 @@
         <v>1070</v>
       </c>
       <c r="U77" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="V77" t="s">
-        <v>897</v>
+        <v>1580</v>
       </c>
       <c r="W77">
         <v>1</v>
@@ -11433,7 +11505,7 @@
         <v>44</v>
       </c>
       <c r="T80" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="U80" t="s">
         <v>79</v>
@@ -11514,10 +11586,10 @@
         <v>89</v>
       </c>
       <c r="U81" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="V81" t="s">
-        <v>1012</v>
+        <v>1575</v>
       </c>
       <c r="W81">
         <v>0</v>
@@ -11592,13 +11664,13 @@
         <v>44</v>
       </c>
       <c r="T82" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="U82" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="V82" t="s">
-        <v>98</v>
+        <v>1581</v>
       </c>
       <c r="W82">
         <v>0</v>
@@ -11655,7 +11727,7 @@
         <v>271</v>
       </c>
       <c r="M83" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N83" t="s">
         <v>67</v>
@@ -11679,7 +11751,7 @@
         <v>1060</v>
       </c>
       <c r="U83" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="V83" t="s">
         <v>977</v>
@@ -11766,7 +11838,7 @@
         <v>1060</v>
       </c>
       <c r="U84" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="V84" t="s">
         <v>574</v>
@@ -11844,7 +11916,7 @@
         <v>687</v>
       </c>
       <c r="U85" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="V85" t="s">
         <v>58</v>
@@ -11916,10 +11988,10 @@
         <v>1072</v>
       </c>
       <c r="U86" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="V86" t="s">
-        <v>1526</v>
+        <v>1582</v>
       </c>
       <c r="W86">
         <v>0</v>
@@ -12087,7 +12159,7 @@
         <v>1065</v>
       </c>
       <c r="U88" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="V88" t="s">
         <v>386</v>
@@ -12255,7 +12327,7 @@
         <v>943</v>
       </c>
       <c r="V90" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="W90">
         <v>0</v>
@@ -12333,7 +12405,7 @@
         <v>1065</v>
       </c>
       <c r="U91" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="V91" t="s">
         <v>373</v>
@@ -12411,7 +12483,7 @@
         <v>955</v>
       </c>
       <c r="V92" t="s">
-        <v>618</v>
+        <v>1591</v>
       </c>
       <c r="W92">
         <v>1</v>
@@ -12462,7 +12534,7 @@
         <v>14</v>
       </c>
       <c r="M93" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N93" t="s">
         <v>67</v>
@@ -12486,7 +12558,7 @@
         <v>912</v>
       </c>
       <c r="V93" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="W93">
         <v>1</v>
@@ -12564,10 +12636,10 @@
         <v>393</v>
       </c>
       <c r="U94" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="V94" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="W94">
         <v>1</v>
@@ -12885,10 +12957,10 @@
         <v>1073</v>
       </c>
       <c r="U98" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="V98" t="s">
-        <v>510</v>
+        <v>1573</v>
       </c>
       <c r="W98">
         <v>1</v>
@@ -13038,10 +13110,10 @@
         <v>1061</v>
       </c>
       <c r="U100" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="V100" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="W100">
         <v>0</v>
@@ -13119,7 +13191,7 @@
         <v>793</v>
       </c>
       <c r="V101" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="W101">
         <v>0</v>
@@ -13272,7 +13344,7 @@
         <v>1066</v>
       </c>
       <c r="U103" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="V103" t="s">
         <v>58</v>
@@ -13437,7 +13509,7 @@
         <v>1070</v>
       </c>
       <c r="U105" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="V105" t="s">
         <v>678</v>
@@ -13566,7 +13638,7 @@
         <v>401</v>
       </c>
       <c r="M107" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N107" t="s">
         <v>29</v>
@@ -13641,7 +13713,7 @@
         <v>822</v>
       </c>
       <c r="M108" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N108" t="s">
         <v>29</v>
@@ -13737,7 +13809,7 @@
         <v>44</v>
       </c>
       <c r="T109" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="U109" t="s">
         <v>263</v>
@@ -14142,7 +14214,7 @@
         <v>830</v>
       </c>
       <c r="V114" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="W114">
         <v>0</v>
@@ -14217,7 +14289,7 @@
         <v>1060</v>
       </c>
       <c r="U115" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="V115" t="s">
         <v>805</v>
@@ -14301,7 +14373,7 @@
         <v>1060</v>
       </c>
       <c r="U116" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="V116" t="s">
         <v>130</v>
@@ -14430,7 +14502,7 @@
         <v>866</v>
       </c>
       <c r="M118" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N118" t="s">
         <v>67</v>
@@ -14574,7 +14646,7 @@
         <v>401</v>
       </c>
       <c r="M120" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N120" t="s">
         <v>29</v>
@@ -14598,7 +14670,7 @@
         <v>402</v>
       </c>
       <c r="V120" t="s">
-        <v>403</v>
+        <v>1576</v>
       </c>
       <c r="W120">
         <v>0</v>
@@ -14751,7 +14823,7 @@
         <v>1062</v>
       </c>
       <c r="U122" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="V122" t="s">
         <v>58</v>
@@ -14847,7 +14919,7 @@
         <v>789</v>
       </c>
       <c r="AB123" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="AC123" t="s">
         <v>122</v>
@@ -14907,7 +14979,7 @@
         <v>1063</v>
       </c>
       <c r="U124" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="V124" t="s">
         <v>293</v>
@@ -15054,7 +15126,7 @@
         <v>401</v>
       </c>
       <c r="M126" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N126" t="s">
         <v>29</v>
@@ -15078,7 +15150,7 @@
         <v>541</v>
       </c>
       <c r="V126" t="s">
-        <v>542</v>
+        <v>1593</v>
       </c>
       <c r="W126">
         <v>0</v>
@@ -15282,7 +15354,7 @@
         <v>1035</v>
       </c>
       <c r="M129" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
@@ -15306,7 +15378,7 @@
         <v>1036</v>
       </c>
       <c r="V129" t="s">
-        <v>510</v>
+        <v>1573</v>
       </c>
       <c r="W129">
         <v>0</v>
@@ -15357,7 +15429,7 @@
         <v>41</v>
       </c>
       <c r="M130" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="N130" t="s">
         <v>67</v>
@@ -15495,7 +15567,7 @@
         <v>23</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="G132" t="s">
         <v>1046</v>
@@ -15621,7 +15693,7 @@
         <v>877</v>
       </c>
       <c r="V133" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="W133">
         <v>0</v>
@@ -15693,7 +15765,7 @@
         <v>1060</v>
       </c>
       <c r="U134" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="V134" t="s">
         <v>314</v>
@@ -16083,7 +16155,7 @@
         <v>509</v>
       </c>
       <c r="V139" t="s">
-        <v>510</v>
+        <v>1573</v>
       </c>
       <c r="W139">
         <v>0</v>
@@ -16239,7 +16311,7 @@
         <v>1068</v>
       </c>
       <c r="U141" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="V141" t="s">
         <v>314</v>
@@ -16299,7 +16371,7 @@
         <v>401</v>
       </c>
       <c r="M142" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N142" t="s">
         <v>67</v>
@@ -16323,7 +16395,7 @@
         <v>1058</v>
       </c>
       <c r="U142" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="V142" t="s">
         <v>589</v>
@@ -16407,7 +16479,7 @@
         <v>1054</v>
       </c>
       <c r="V143" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="W143">
         <v>1</v>
@@ -16427,10 +16499,10 @@
     </row>
     <row r="144" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B144" t="s">
         <v>1275</v>
-      </c>
-      <c r="B144" t="s">
-        <v>1276</v>
       </c>
       <c r="D144">
         <v>2018</v>
@@ -16440,10 +16512,10 @@
         <v>2</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="G144" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="H144" t="s">
         <v>105</v>
@@ -16482,16 +16554,16 @@
         <v>1076</v>
       </c>
       <c r="U144" t="s">
+        <v>1277</v>
+      </c>
+      <c r="V144" t="s">
         <v>1278</v>
       </c>
-      <c r="V144" t="s">
+      <c r="Y144">
+        <v>1</v>
+      </c>
+      <c r="AA144" t="s">
         <v>1279</v>
-      </c>
-      <c r="Y144">
-        <v>1</v>
-      </c>
-      <c r="AA144" t="s">
-        <v>1280</v>
       </c>
       <c r="AC144" t="s">
         <v>35</v>
@@ -16499,7 +16571,7 @@
     </row>
     <row r="145" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B145" t="s">
         <v>170</v>
@@ -16515,10 +16587,10 @@
         <v>0</v>
       </c>
       <c r="F145" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G145" t="s">
         <v>1296</v>
-      </c>
-      <c r="G145" t="s">
-        <v>1297</v>
       </c>
       <c r="H145" t="s">
         <v>52</v>
@@ -16554,7 +16626,7 @@
         <v>1058</v>
       </c>
       <c r="U145" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="V145" t="s">
         <v>481</v>
@@ -16563,7 +16635,7 @@
         <v>0</v>
       </c>
       <c r="AA145" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="AB145" t="s">
         <v>141</v>
@@ -16574,10 +16646,10 @@
     </row>
     <row r="146" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B146" t="s">
         <v>1281</v>
-      </c>
-      <c r="B146" t="s">
-        <v>1282</v>
       </c>
       <c r="C146" t="s">
         <v>75</v>
@@ -16590,10 +16662,10 @@
         <v>2</v>
       </c>
       <c r="F146" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G146" t="s">
         <v>1283</v>
-      </c>
-      <c r="G146" t="s">
-        <v>1284</v>
       </c>
       <c r="H146" t="s">
         <v>52</v>
@@ -16608,7 +16680,7 @@
         <v>210</v>
       </c>
       <c r="M146" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="N146" t="s">
         <v>29</v>
@@ -16632,16 +16704,16 @@
         <v>1078</v>
       </c>
       <c r="U146" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="V146" t="s">
+        <v>1594</v>
+      </c>
+      <c r="Y146">
+        <v>0</v>
+      </c>
+      <c r="AA146" t="s">
         <v>1286</v>
-      </c>
-      <c r="Y146">
-        <v>0</v>
-      </c>
-      <c r="AA146" t="s">
-        <v>1287</v>
       </c>
       <c r="AC146" t="s">
         <v>35</v>
@@ -16649,7 +16721,7 @@
     </row>
     <row r="147" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B147" t="s">
         <v>170</v>
@@ -16665,10 +16737,10 @@
         <v>3</v>
       </c>
       <c r="F147" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G147" t="s">
         <v>1269</v>
-      </c>
-      <c r="G147" t="s">
-        <v>1270</v>
       </c>
       <c r="H147" t="s">
         <v>105</v>
@@ -16680,10 +16752,10 @@
         <v>731</v>
       </c>
       <c r="L147" t="s">
+        <v>1270</v>
+      </c>
+      <c r="M147" t="s">
         <v>1271</v>
-      </c>
-      <c r="M147" t="s">
-        <v>1272</v>
       </c>
       <c r="N147" t="s">
         <v>29</v>
@@ -16704,16 +16776,16 @@
         <v>1061</v>
       </c>
       <c r="U147" t="s">
+        <v>1272</v>
+      </c>
+      <c r="V147" t="s">
+        <v>1591</v>
+      </c>
+      <c r="Y147">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="s">
         <v>1273</v>
-      </c>
-      <c r="V147" t="s">
-        <v>618</v>
-      </c>
-      <c r="Y147">
-        <v>0</v>
-      </c>
-      <c r="AA147" t="s">
-        <v>1274</v>
       </c>
       <c r="AC147" t="s">
         <v>35</v>
@@ -16721,7 +16793,7 @@
     </row>
     <row r="148" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B148" t="s">
         <v>91</v>
@@ -16737,10 +16809,10 @@
         <v>0</v>
       </c>
       <c r="F148" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G148" t="s">
         <v>1307</v>
-      </c>
-      <c r="G148" t="s">
-        <v>1308</v>
       </c>
       <c r="H148" t="s">
         <v>147</v>
@@ -16752,10 +16824,10 @@
         <v>1571</v>
       </c>
       <c r="L148" t="s">
+        <v>1308</v>
+      </c>
+      <c r="M148" t="s">
         <v>1309</v>
-      </c>
-      <c r="M148" t="s">
-        <v>1310</v>
       </c>
       <c r="N148" t="s">
         <v>158</v>
@@ -16779,7 +16851,7 @@
         <v>1063</v>
       </c>
       <c r="U148" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="V148" t="s">
         <v>58</v>
@@ -16796,13 +16868,13 @@
     </row>
     <row r="149" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B149" t="s">
         <v>287</v>
       </c>
       <c r="C149" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D149">
         <v>2022</v>
@@ -16812,10 +16884,10 @@
         <v>10</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G149" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="H149" t="s">
         <v>147</v>
@@ -16830,7 +16902,7 @@
         <v>41</v>
       </c>
       <c r="M149" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="N149" t="s">
         <v>29</v>
@@ -16851,16 +16923,16 @@
         <v>393</v>
       </c>
       <c r="U149" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="V149" t="s">
+        <v>1204</v>
+      </c>
+      <c r="Y149">
+        <v>0</v>
+      </c>
+      <c r="AA149" t="s">
         <v>1205</v>
-      </c>
-      <c r="Y149">
-        <v>0</v>
-      </c>
-      <c r="AA149" t="s">
-        <v>1206</v>
       </c>
       <c r="AC149" t="s">
         <v>35</v>
@@ -16868,7 +16940,7 @@
     </row>
     <row r="150" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B150" t="s">
         <v>154</v>
@@ -16881,10 +16953,10 @@
         <v>219</v>
       </c>
       <c r="F150" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G150" t="s">
         <v>1313</v>
-      </c>
-      <c r="G150" t="s">
-        <v>1314</v>
       </c>
       <c r="H150" t="s">
         <v>400</v>
@@ -16899,7 +16971,7 @@
         <v>1035</v>
       </c>
       <c r="M150" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N150" t="s">
         <v>29</v>
@@ -16926,13 +16998,13 @@
         <v>510</v>
       </c>
       <c r="V150" t="s">
-        <v>510</v>
+        <v>1573</v>
       </c>
       <c r="Y150">
         <v>0</v>
       </c>
       <c r="AB150" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="AC150" t="s">
         <v>35</v>
@@ -16940,7 +17012,7 @@
     </row>
     <row r="151" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B151" t="s">
         <v>37</v>
@@ -16956,16 +17028,16 @@
         <v>3</v>
       </c>
       <c r="F151" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G151" t="s">
         <v>1257</v>
-      </c>
-      <c r="G151" t="s">
-        <v>1258</v>
       </c>
       <c r="H151" t="s">
         <v>26</v>
       </c>
       <c r="I151" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J151">
         <v>11528750</v>
@@ -16989,7 +17061,7 @@
         <v>1</v>
       </c>
       <c r="Q151" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -17001,10 +17073,10 @@
         <v>1070</v>
       </c>
       <c r="U151" t="s">
+        <v>1259</v>
+      </c>
+      <c r="V151" t="s">
         <v>1260</v>
-      </c>
-      <c r="V151" t="s">
-        <v>1261</v>
       </c>
       <c r="Y151">
         <v>1</v>
@@ -17018,13 +17090,13 @@
     </row>
     <row r="152" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B152" t="s">
         <v>287</v>
       </c>
       <c r="C152" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D152">
         <v>2018</v>
@@ -17034,10 +17106,10 @@
         <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="G152" t="s">
         <v>1264</v>
-      </c>
-      <c r="G152" t="s">
-        <v>1265</v>
       </c>
       <c r="H152" t="s">
         <v>105</v>
@@ -17073,16 +17145,16 @@
         <v>1064</v>
       </c>
       <c r="U152" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="V152" t="s">
+        <v>1265</v>
+      </c>
+      <c r="Y152">
+        <v>0</v>
+      </c>
+      <c r="AB152" t="s">
         <v>1266</v>
-      </c>
-      <c r="Y152">
-        <v>0</v>
-      </c>
-      <c r="AB152" t="s">
-        <v>1267</v>
       </c>
       <c r="AC152" t="s">
         <v>35</v>
@@ -17090,7 +17162,7 @@
     </row>
     <row r="153" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B153" t="s">
         <v>37</v>
@@ -17106,10 +17178,10 @@
         <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G153" t="s">
         <v>1233</v>
-      </c>
-      <c r="G153" t="s">
-        <v>1234</v>
       </c>
       <c r="H153" t="s">
         <v>147</v>
@@ -17148,16 +17220,16 @@
         <v>1059</v>
       </c>
       <c r="U153" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="V153" t="s">
+        <v>1583</v>
+      </c>
+      <c r="Y153">
+        <v>1</v>
+      </c>
+      <c r="AA153" t="s">
         <v>1235</v>
-      </c>
-      <c r="Y153">
-        <v>1</v>
-      </c>
-      <c r="AA153" t="s">
-        <v>1236</v>
       </c>
       <c r="AC153" t="s">
         <v>35</v>
@@ -17165,7 +17237,7 @@
     </row>
     <row r="154" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B154" t="s">
         <v>37</v>
@@ -17181,16 +17253,16 @@
         <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G154" t="s">
         <v>1220</v>
-      </c>
-      <c r="G154" t="s">
-        <v>1221</v>
       </c>
       <c r="H154" t="s">
         <v>26</v>
       </c>
       <c r="I154" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J154">
         <v>151682564</v>
@@ -17199,7 +17271,7 @@
         <v>366</v>
       </c>
       <c r="L154" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M154" t="s">
         <v>485</v>
@@ -17226,10 +17298,10 @@
         <v>687</v>
       </c>
       <c r="U154" t="s">
+        <v>1223</v>
+      </c>
+      <c r="V154" t="s">
         <v>1224</v>
-      </c>
-      <c r="V154" t="s">
-        <v>1225</v>
       </c>
       <c r="Y154">
         <v>0</v>
@@ -17240,7 +17312,7 @@
     </row>
     <row r="155" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B155" t="s">
         <v>154</v>
@@ -17256,10 +17328,10 @@
         <v>3</v>
       </c>
       <c r="F155" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G155" t="s">
         <v>1248</v>
-      </c>
-      <c r="G155" t="s">
-        <v>1249</v>
       </c>
       <c r="H155" t="s">
         <v>147</v>
@@ -17271,7 +17343,7 @@
         <v>1096</v>
       </c>
       <c r="L155" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="M155" t="s">
         <v>918</v>
@@ -17304,7 +17376,7 @@
         <v>1</v>
       </c>
       <c r="AA155" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="AB155" t="s">
         <v>405</v>
@@ -17315,7 +17387,7 @@
     </row>
     <row r="156" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B156" t="s">
         <v>37</v>
@@ -17331,16 +17403,16 @@
         <v>3</v>
       </c>
       <c r="F156" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G156" t="s">
         <v>1253</v>
-      </c>
-      <c r="G156" t="s">
-        <v>1254</v>
       </c>
       <c r="H156" t="s">
         <v>26</v>
       </c>
       <c r="I156" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J156">
         <v>69194428</v>
@@ -17376,10 +17448,10 @@
         <v>1070</v>
       </c>
       <c r="U156" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="V156" t="s">
-        <v>1255</v>
+        <v>1584</v>
       </c>
       <c r="Y156">
         <v>1</v>
@@ -17390,7 +17462,7 @@
     </row>
     <row r="157" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B157" t="s">
         <v>249</v>
@@ -17406,10 +17478,10 @@
         <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G157" t="s">
         <v>1227</v>
-      </c>
-      <c r="G157" t="s">
-        <v>1228</v>
       </c>
       <c r="H157" t="s">
         <v>26</v>
@@ -17439,7 +17511,7 @@
         <v>1</v>
       </c>
       <c r="Q157" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="R157">
         <v>0</v>
@@ -17451,16 +17523,16 @@
         <v>26</v>
       </c>
       <c r="U157" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="V157" t="s">
+        <v>1585</v>
+      </c>
+      <c r="Y157">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="s">
         <v>1230</v>
-      </c>
-      <c r="Y157">
-        <v>0</v>
-      </c>
-      <c r="AA157" t="s">
-        <v>1231</v>
       </c>
       <c r="AC157" t="s">
         <v>35</v>
@@ -17468,10 +17540,10 @@
     </row>
     <row r="158" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B158" t="s">
         <v>1186</v>
-      </c>
-      <c r="B158" t="s">
-        <v>1187</v>
       </c>
       <c r="C158" t="s">
         <v>49</v>
@@ -17484,10 +17556,10 @@
         <v>12</v>
       </c>
       <c r="F158" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G158" t="s">
         <v>1188</v>
-      </c>
-      <c r="G158" t="s">
-        <v>1189</v>
       </c>
       <c r="H158" t="s">
         <v>105</v>
@@ -17499,10 +17571,10 @@
         <v>395</v>
       </c>
       <c r="L158" t="s">
+        <v>1189</v>
+      </c>
+      <c r="M158" t="s">
         <v>1190</v>
-      </c>
-      <c r="M158" t="s">
-        <v>1191</v>
       </c>
       <c r="N158" t="s">
         <v>29</v>
@@ -17520,7 +17592,7 @@
         <v>44</v>
       </c>
       <c r="T158" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="U158" t="s">
         <v>193</v>
@@ -17532,7 +17604,7 @@
         <v>0</v>
       </c>
       <c r="AA158" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="AB158" t="s">
         <v>247</v>
@@ -17543,13 +17615,13 @@
     </row>
     <row r="159" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B159" t="s">
         <v>114</v>
       </c>
       <c r="C159" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D159">
         <v>2022</v>
@@ -17559,10 +17631,10 @@
         <v>16</v>
       </c>
       <c r="F159" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G159" t="s">
         <v>1196</v>
-      </c>
-      <c r="G159" t="s">
-        <v>1197</v>
       </c>
       <c r="H159" t="s">
         <v>26</v>
@@ -17577,7 +17649,7 @@
         <v>2</v>
       </c>
       <c r="L159" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="M159" t="s">
         <v>84</v>
@@ -17601,16 +17673,16 @@
         <v>1068</v>
       </c>
       <c r="U159" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="V159" t="s">
+        <v>1198</v>
+      </c>
+      <c r="Y159">
+        <v>1</v>
+      </c>
+      <c r="AA159" t="s">
         <v>1199</v>
-      </c>
-      <c r="Y159">
-        <v>1</v>
-      </c>
-      <c r="AA159" t="s">
-        <v>1200</v>
       </c>
       <c r="AC159" t="s">
         <v>316</v>
@@ -17618,10 +17690,10 @@
     </row>
     <row r="160" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B160" t="s">
         <v>1288</v>
-      </c>
-      <c r="B160" t="s">
-        <v>1289</v>
       </c>
       <c r="C160" t="s">
         <v>49</v>
@@ -17634,16 +17706,16 @@
         <v>2</v>
       </c>
       <c r="F160" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G160" t="s">
         <v>1290</v>
-      </c>
-      <c r="G160" t="s">
-        <v>1291</v>
       </c>
       <c r="H160" t="s">
         <v>26</v>
       </c>
       <c r="I160" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J160">
         <v>9855657663</v>
@@ -17661,7 +17733,7 @@
         <v>0</v>
       </c>
       <c r="Q160" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="R160">
         <v>0</v>
@@ -17673,10 +17745,10 @@
         <v>1070</v>
       </c>
       <c r="U160" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="V160" t="s">
-        <v>1294</v>
+        <v>1586</v>
       </c>
       <c r="Y160">
         <v>1</v>
@@ -17690,7 +17762,7 @@
     </row>
     <row r="161" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B161" t="s">
         <v>37</v>
@@ -17706,10 +17778,10 @@
         <v>22</v>
       </c>
       <c r="F161" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G161" t="s">
         <v>1166</v>
-      </c>
-      <c r="G161" t="s">
-        <v>1167</v>
       </c>
       <c r="H161" t="s">
         <v>400</v>
@@ -17748,16 +17820,16 @@
         <v>1077</v>
       </c>
       <c r="U161" t="s">
+        <v>1522</v>
+      </c>
+      <c r="V161" t="s">
         <v>1523</v>
       </c>
-      <c r="V161" t="s">
-        <v>1524</v>
-      </c>
       <c r="Y161">
         <v>1</v>
       </c>
       <c r="AA161" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="AC161" t="s">
         <v>35</v>
@@ -17765,13 +17837,13 @@
     </row>
     <row r="162" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B162" t="s">
         <v>1170</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>1171</v>
-      </c>
-      <c r="C162" t="s">
-        <v>1172</v>
       </c>
       <c r="D162">
         <v>2023</v>
@@ -17781,10 +17853,10 @@
         <v>17</v>
       </c>
       <c r="F162" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G162" t="s">
         <v>1173</v>
-      </c>
-      <c r="G162" t="s">
-        <v>1174</v>
       </c>
       <c r="H162" t="s">
         <v>147</v>
@@ -17796,16 +17868,16 @@
         <v>152</v>
       </c>
       <c r="M162" t="s">
+        <v>1174</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>1</v>
+      </c>
+      <c r="Q162" t="s">
         <v>1175</v>
-      </c>
-      <c r="O162">
-        <v>0</v>
-      </c>
-      <c r="P162">
-        <v>1</v>
-      </c>
-      <c r="Q162" t="s">
-        <v>1176</v>
       </c>
       <c r="R162">
         <v>0</v>
@@ -17817,10 +17889,10 @@
         <v>1064</v>
       </c>
       <c r="U162" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="V162" t="s">
-        <v>1178</v>
+        <v>1587</v>
       </c>
       <c r="Y162">
         <v>1</v>
@@ -17834,7 +17906,7 @@
     </row>
     <row r="163" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B163" t="s">
         <v>91</v>
@@ -17850,10 +17922,10 @@
         <v>63</v>
       </c>
       <c r="F163" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G163" t="s">
         <v>1143</v>
-      </c>
-      <c r="G163" t="s">
-        <v>1144</v>
       </c>
       <c r="H163" t="s">
         <v>105</v>
@@ -17889,16 +17961,16 @@
         <v>1066</v>
       </c>
       <c r="U163" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="V163" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="Y163">
         <v>0</v>
       </c>
       <c r="AA163" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="AB163" t="s">
         <v>141</v>
@@ -17909,7 +17981,7 @@
     </row>
     <row r="164" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B164" t="s">
         <v>249</v>
@@ -17925,10 +17997,10 @@
         <v>90</v>
       </c>
       <c r="F164" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G164" t="s">
         <v>1138</v>
-      </c>
-      <c r="G164" t="s">
-        <v>1139</v>
       </c>
       <c r="H164" t="s">
         <v>26</v>
@@ -17943,7 +18015,7 @@
         <v>190</v>
       </c>
       <c r="M164" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="N164" t="s">
         <v>158</v>
@@ -17967,16 +18039,16 @@
         <v>1068</v>
       </c>
       <c r="U164" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="V164" t="s">
+        <v>1139</v>
+      </c>
+      <c r="Y164">
+        <v>1</v>
+      </c>
+      <c r="AA164" t="s">
         <v>1140</v>
-      </c>
-      <c r="Y164">
-        <v>1</v>
-      </c>
-      <c r="AA164" t="s">
-        <v>1141</v>
       </c>
       <c r="AC164" t="s">
         <v>316</v>
@@ -17984,10 +18056,10 @@
     </row>
     <row r="165" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B165" t="s">
         <v>1152</v>
-      </c>
-      <c r="B165" t="s">
-        <v>1153</v>
       </c>
       <c r="C165" t="s">
         <v>63</v>
@@ -18000,10 +18072,10 @@
         <v>33</v>
       </c>
       <c r="F165" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G165" t="s">
         <v>1154</v>
-      </c>
-      <c r="G165" t="s">
-        <v>1155</v>
       </c>
       <c r="H165" t="s">
         <v>147</v>
@@ -18015,10 +18087,10 @@
         <v>183</v>
       </c>
       <c r="L165" t="s">
+        <v>1155</v>
+      </c>
+      <c r="M165" t="s">
         <v>1156</v>
-      </c>
-      <c r="M165" t="s">
-        <v>1157</v>
       </c>
       <c r="O165">
         <v>1</v>
@@ -18036,7 +18108,7 @@
         <v>1060</v>
       </c>
       <c r="U165" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="V165" t="s">
         <v>984</v>
@@ -18053,7 +18125,7 @@
     </row>
     <row r="166" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B166" t="s">
         <v>74</v>
@@ -18069,10 +18141,10 @@
         <v>16</v>
       </c>
       <c r="F166" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G166" t="s">
         <v>1184</v>
-      </c>
-      <c r="G166" t="s">
-        <v>1185</v>
       </c>
       <c r="H166" t="s">
         <v>105</v>
@@ -18108,10 +18180,10 @@
         <v>1066</v>
       </c>
       <c r="U166" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="V166" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="Y166">
         <v>0</v>
@@ -18125,7 +18197,7 @@
     </row>
     <row r="167" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B167" t="s">
         <v>170</v>
@@ -18141,10 +18213,10 @@
         <v>10</v>
       </c>
       <c r="F167" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G167" t="s">
         <v>1214</v>
-      </c>
-      <c r="G167" t="s">
-        <v>1215</v>
       </c>
       <c r="H167" t="s">
         <v>147</v>
@@ -18159,7 +18231,7 @@
         <v>242</v>
       </c>
       <c r="M167" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="N167" t="s">
         <v>29</v>
@@ -18180,16 +18252,16 @@
         <v>1060</v>
       </c>
       <c r="U167" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="V167" t="s">
+        <v>1216</v>
+      </c>
+      <c r="Y167">
+        <v>0</v>
+      </c>
+      <c r="AA167" t="s">
         <v>1217</v>
-      </c>
-      <c r="Y167">
-        <v>0</v>
-      </c>
-      <c r="AA167" t="s">
-        <v>1218</v>
       </c>
       <c r="AC167" t="s">
         <v>35</v>
@@ -18197,7 +18269,7 @@
     </row>
     <row r="168" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B168" t="s">
         <v>37</v>
@@ -18213,10 +18285,10 @@
         <v>7</v>
       </c>
       <c r="F168" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G168" t="s">
         <v>1147</v>
-      </c>
-      <c r="G168" t="s">
-        <v>1148</v>
       </c>
       <c r="H168" t="s">
         <v>26</v>
@@ -18234,7 +18306,7 @@
         <v>27</v>
       </c>
       <c r="M168" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N168" t="s">
         <v>158</v>
@@ -18246,7 +18318,7 @@
         <v>1</v>
       </c>
       <c r="Q168" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="R168">
         <v>0</v>
@@ -18258,10 +18330,10 @@
         <v>1070</v>
       </c>
       <c r="U168" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="V168" t="s">
-        <v>1151</v>
+        <v>1588</v>
       </c>
       <c r="Y168">
         <v>0</v>
@@ -18275,7 +18347,7 @@
     </row>
     <row r="169" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B169" t="s">
         <v>249</v>
@@ -18291,10 +18363,10 @@
         <v>27</v>
       </c>
       <c r="F169" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G169" t="s">
         <v>1160</v>
-      </c>
-      <c r="G169" t="s">
-        <v>1161</v>
       </c>
       <c r="H169" t="s">
         <v>147</v>
@@ -18306,10 +18378,10 @@
         <v>638</v>
       </c>
       <c r="L169" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M169" t="s">
         <v>1162</v>
-      </c>
-      <c r="M169" t="s">
-        <v>1163</v>
       </c>
       <c r="N169" t="s">
         <v>29</v>
@@ -18333,10 +18405,10 @@
         <v>1068</v>
       </c>
       <c r="U169" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="V169" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="Y169">
         <v>0</v>
@@ -18350,7 +18422,7 @@
     </row>
     <row r="170" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B170" t="s">
         <v>37</v>
@@ -18366,10 +18438,10 @@
         <v>5</v>
       </c>
       <c r="F170" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G170" t="s">
         <v>1243</v>
-      </c>
-      <c r="G170" t="s">
-        <v>1244</v>
       </c>
       <c r="H170" t="s">
         <v>105</v>
@@ -18384,7 +18456,7 @@
         <v>53</v>
       </c>
       <c r="M170" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="N170" t="s">
         <v>29</v>
@@ -18405,10 +18477,10 @@
         <v>1060</v>
       </c>
       <c r="U170" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="V170" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="Y170">
         <v>0</v>
@@ -18425,7 +18497,7 @@
         <v>197</v>
       </c>
       <c r="B171" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C171" t="s">
         <v>75</v>
@@ -18438,16 +18510,16 @@
         <v>15</v>
       </c>
       <c r="F171" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G171" t="s">
         <v>1180</v>
-      </c>
-      <c r="G171" t="s">
-        <v>1181</v>
       </c>
       <c r="H171" t="s">
         <v>26</v>
       </c>
       <c r="I171" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="J171">
         <v>468596472</v>
@@ -18459,7 +18531,7 @@
         <v>27</v>
       </c>
       <c r="M171" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="N171" t="s">
         <v>158</v>
@@ -18497,13 +18569,13 @@
     </row>
     <row r="172" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B172" t="s">
         <v>278</v>
       </c>
       <c r="C172" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D172">
         <v>2023</v>
@@ -18513,10 +18585,10 @@
         <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G172" t="s">
         <v>1209</v>
-      </c>
-      <c r="G172" t="s">
-        <v>1210</v>
       </c>
       <c r="H172" t="s">
         <v>147</v>
@@ -18531,7 +18603,7 @@
         <v>27</v>
       </c>
       <c r="M172" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="N172" t="s">
         <v>158</v>
@@ -18552,7 +18624,7 @@
         <v>1060</v>
       </c>
       <c r="U172" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="V172" t="s">
         <v>373</v>
@@ -18566,7 +18638,7 @@
     </row>
     <row r="173" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B173" t="s">
         <v>187</v>
@@ -18582,10 +18654,10 @@
         <v>7</v>
       </c>
       <c r="F173" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G173" t="s">
         <v>1238</v>
-      </c>
-      <c r="G173" t="s">
-        <v>1239</v>
       </c>
       <c r="H173" t="s">
         <v>147</v>
@@ -18600,7 +18672,7 @@
         <v>41</v>
       </c>
       <c r="M173" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="N173" t="s">
         <v>158</v>
@@ -18612,7 +18684,7 @@
         <v>1</v>
       </c>
       <c r="Q173" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -18627,7 +18699,7 @@
         <v>46</v>
       </c>
       <c r="V173" t="s">
-        <v>46</v>
+        <v>1578</v>
       </c>
       <c r="Y173">
         <v>1</v>
@@ -18641,13 +18713,13 @@
     </row>
     <row r="174" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B174" t="s">
         <v>1115</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>1116</v>
-      </c>
-      <c r="C174" t="s">
-        <v>1117</v>
       </c>
       <c r="D174">
         <v>2023</v>
@@ -18657,10 +18729,10 @@
         <v>7</v>
       </c>
       <c r="F174" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G174" t="s">
         <v>1118</v>
-      </c>
-      <c r="G174" t="s">
-        <v>1119</v>
       </c>
       <c r="H174" t="s">
         <v>105</v>
@@ -18699,16 +18771,16 @@
         <v>1066</v>
       </c>
       <c r="U174" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="V174" t="s">
+        <v>1119</v>
+      </c>
+      <c r="Y174">
+        <v>1</v>
+      </c>
+      <c r="AA174" t="s">
         <v>1120</v>
-      </c>
-      <c r="Y174">
-        <v>1</v>
-      </c>
-      <c r="AA174" t="s">
-        <v>1121</v>
       </c>
       <c r="AC174" t="s">
         <v>35</v>
@@ -18716,10 +18788,10 @@
     </row>
     <row r="175" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B175" t="s">
         <v>1128</v>
-      </c>
-      <c r="B175" t="s">
-        <v>1129</v>
       </c>
       <c r="C175" t="s">
         <v>199</v>
@@ -18732,10 +18804,10 @@
         <v>121</v>
       </c>
       <c r="F175" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G175" t="s">
         <v>1130</v>
-      </c>
-      <c r="G175" t="s">
-        <v>1131</v>
       </c>
       <c r="H175" t="s">
         <v>147</v>
@@ -18747,10 +18819,10 @@
         <v>92</v>
       </c>
       <c r="L175" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M175" t="s">
         <v>1132</v>
-      </c>
-      <c r="M175" t="s">
-        <v>1133</v>
       </c>
       <c r="N175" t="s">
         <v>158</v>
@@ -18774,16 +18846,16 @@
         <v>1064</v>
       </c>
       <c r="U175" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="V175" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Y175">
         <v>0</v>
       </c>
       <c r="AA175" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AC175" t="s">
         <v>35</v>
@@ -18791,13 +18863,13 @@
     </row>
     <row r="176" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B176" t="s">
         <v>1122</v>
       </c>
-      <c r="B176" t="s">
-        <v>1123</v>
-      </c>
       <c r="C176" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D176">
         <v>2023</v>
@@ -18807,10 +18879,10 @@
         <v>128</v>
       </c>
       <c r="F176" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G176" t="s">
         <v>1124</v>
-      </c>
-      <c r="G176" t="s">
-        <v>1125</v>
       </c>
       <c r="H176" t="s">
         <v>147</v>
@@ -18825,7 +18897,7 @@
         <v>27</v>
       </c>
       <c r="M176" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="N176" t="s">
         <v>29</v>
@@ -18846,10 +18918,10 @@
         <v>1076</v>
       </c>
       <c r="U176" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="V176" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Y176">
         <v>1</v>
@@ -18863,7 +18935,7 @@
     </row>
     <row r="177" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B177" t="s">
         <v>170</v>
@@ -18879,10 +18951,10 @@
         <v>0</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G177" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="H177" t="s">
         <v>400</v>
@@ -18894,10 +18966,10 @@
         <v>600</v>
       </c>
       <c r="L177" t="s">
+        <v>1301</v>
+      </c>
+      <c r="M177" t="s">
         <v>1302</v>
-      </c>
-      <c r="M177" t="s">
-        <v>1303</v>
       </c>
       <c r="N177" t="s">
         <v>29</v>
@@ -18921,7 +18993,7 @@
         <v>1078</v>
       </c>
       <c r="U177" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="V177" t="s">
         <v>30</v>
@@ -18930,7 +19002,7 @@
         <v>0</v>
       </c>
       <c r="AA177" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="AC177" t="s">
         <v>35</v>
@@ -18957,7 +19029,7 @@
   <sheetData>
     <row r="1" spans="3:31" x14ac:dyDescent="0.2">
       <c r="P1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="W1" t="s">
         <v>9</v>
@@ -19076,7 +19148,7 @@
         <v>Bogotá, Colombia</v>
       </c>
       <c r="AD5" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AE5">
         <v>2</v>
@@ -19119,10 +19191,10 @@
         <v>Anomaly detection</v>
       </c>
       <c r="P7" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q7" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="R7" t="str">
         <v>Optimization</v>
@@ -19142,7 +19214,7 @@
     </row>
     <row r="8" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C8" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="G8" t="str">
         <v>ARIMA</v>
@@ -19192,7 +19264,7 @@
         <v>Chengdu, China</v>
       </c>
       <c r="AD9" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AE9">
         <v>2</v>
@@ -19238,13 +19310,13 @@
         <v>618</v>
       </c>
       <c r="Q11" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="R11" t="str">
         <v>Ranking algorithm</v>
       </c>
       <c r="W11" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="X11" t="str">
         <v>Curitiba, Brazil</v>
@@ -19258,7 +19330,7 @@
     </row>
     <row r="12" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="G12" t="str">
         <v>Bayesian Hierarchical</v>
@@ -19267,7 +19339,7 @@
         <v>138</v>
       </c>
       <c r="Q12" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="R12" t="str">
         <v>Probability model</v>
@@ -19287,7 +19359,7 @@
     </row>
     <row r="13" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="G13" t="str">
         <v>Bayesian model</v>
@@ -19316,7 +19388,7 @@
     </row>
     <row r="14" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C14" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G14" t="str">
         <v>Bidirectional Long short-term memory</v>
@@ -19461,7 +19533,7 @@
     </row>
     <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="G19" t="str">
         <v>Binomial logit model</v>
@@ -19490,7 +19562,7 @@
     </row>
     <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G20" t="str">
         <v>BL</v>
@@ -19519,7 +19591,7 @@
     </row>
     <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="G21" t="str">
         <v>Boarding stop estimation</v>
@@ -19540,7 +19612,7 @@
         <v>Greater Toronto and Hamilton Area, Canada</v>
       </c>
       <c r="AD21" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="AE21">
         <v>18</v>
@@ -19548,7 +19620,7 @@
     </row>
     <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="G22" t="str">
         <v>Broyden-Fletcher-Goldfarb-Shanno</v>
@@ -19577,7 +19649,7 @@
     </row>
     <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G23" t="str">
         <v>Card ID-based analysis</v>
@@ -19664,7 +19736,7 @@
     </row>
     <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G26" t="str">
         <v>Clustering</v>
@@ -19693,7 +19765,7 @@
     </row>
     <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G27" t="str">
         <v>Clustering based on socioeconomics</v>
@@ -19731,7 +19803,7 @@
         <v>58</v>
       </c>
       <c r="Q28" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="R28" t="str">
         <v>Neural networks</v>
@@ -19751,7 +19823,7 @@
     </row>
     <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="G29" t="str">
         <v>Common lines analysis</v>
@@ -19772,7 +19844,7 @@
         <v>Jeonju, South Korea</v>
       </c>
       <c r="AD29" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="AE29">
         <v>8</v>
@@ -19780,7 +19852,7 @@
     </row>
     <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="G30" t="str">
         <v>Conditional Random Fields</v>
@@ -19809,7 +19881,7 @@
     </row>
     <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G31" t="str">
         <v>Continuous user-based model</v>
@@ -19859,7 +19931,7 @@
         <v>Kocaeli, Turkey</v>
       </c>
       <c r="AD32" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="AE32">
         <v>2</v>
@@ -19925,7 +19997,7 @@
     </row>
     <row r="35" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="G35" t="str">
         <v>Data polishing</v>
@@ -19940,7 +20012,7 @@
         <v>Data augmentation</v>
       </c>
       <c r="W35" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="X35" t="str">
         <v>Macao, China</v>
@@ -19954,7 +20026,7 @@
     </row>
     <row r="36" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="G36" t="str">
         <v>Day-to-day variability model</v>
@@ -19983,7 +20055,7 @@
     </row>
     <row r="37" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="G37" t="str">
         <v>DBSACN</v>
@@ -20004,7 +20076,7 @@
         <v>Madrid, Spain</v>
       </c>
       <c r="AD37" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AE37">
         <v>5</v>
@@ -20012,7 +20084,7 @@
     </row>
     <row r="38" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="G38" t="str">
         <v>DBSCAN</v>
@@ -20108,7 +20180,7 @@
         <v>New York, USA</v>
       </c>
       <c r="AD41" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="AE41">
         <v>3</v>
@@ -20134,7 +20206,7 @@
         <v>Osaka, Japan</v>
       </c>
       <c r="AD42" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AE42">
         <v>5</v>
@@ -20142,13 +20214,13 @@
     </row>
     <row r="43" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G43" t="str">
         <v>Densely Connected Convolutional Networks</v>
       </c>
       <c r="P43" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="Q43" t="s">
         <v>193</v>
@@ -20168,7 +20240,7 @@
     </row>
     <row r="44" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="G44" t="str">
         <v>Descriptive statistics</v>
@@ -20180,7 +20252,7 @@
         <v>32</v>
       </c>
       <c r="W44" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="X44" t="str">
         <v>Porto, Portugal</v>
@@ -20212,7 +20284,7 @@
         <v>Qingdao, China</v>
       </c>
       <c r="AD45" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="AE45">
         <v>7</v>
@@ -20307,7 +20379,7 @@
         <v>32</v>
       </c>
       <c r="Q49" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="W49" t="s">
         <v>127</v>
@@ -20324,7 +20396,7 @@
     </row>
     <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="G50" t="str">
         <v>Dynamic programming</v>
@@ -20350,7 +20422,7 @@
     </row>
     <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="G51" t="str">
         <v>Early Warning Framework</v>
@@ -20368,7 +20440,7 @@
         <v>Santiago, Chile</v>
       </c>
       <c r="AD51" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AE51">
         <v>5</v>
@@ -20376,7 +20448,7 @@
     </row>
     <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="G52" t="str">
         <v>EJT framework</v>
@@ -20394,7 +20466,7 @@
         <v>São Paulo, Brazil</v>
       </c>
       <c r="AD52" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AE52">
         <v>8</v>
@@ -20402,7 +20474,7 @@
     </row>
     <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="G53" t="str">
         <v>EM algorithm</v>
@@ -20420,7 +20492,7 @@
         <v>Sejong City, South Korea</v>
       </c>
       <c r="AD53" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="AE53">
         <v>0</v>
@@ -20454,7 +20526,7 @@
     </row>
     <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="G55" t="str">
         <v>Extraction of Activity Types and Change Detection</v>
@@ -20480,7 +20552,7 @@
     </row>
     <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G56" t="str">
         <v>Fixed effects</v>
@@ -20524,7 +20596,7 @@
         <v>Shenzhen, China</v>
       </c>
       <c r="AD57" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="AE57">
         <v>11</v>
@@ -20532,7 +20604,7 @@
     </row>
     <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G58" t="str">
         <v>Framework for Recognizing transfer passengers</v>
@@ -20544,7 +20616,7 @@
         <v>816</v>
       </c>
       <c r="W58" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="X58" t="str">
         <v>Shenzhen, China;Hangzhou, China</v>
@@ -20558,7 +20630,7 @@
     </row>
     <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="G59" t="str">
         <v>Fully connected network</v>
@@ -20584,7 +20656,7 @@
     </row>
     <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G60" t="str">
         <v>Gaussian mixture model</v>
@@ -20610,7 +20682,7 @@
     </row>
     <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G61" t="str">
         <v>Gaussian Process Regressor</v>
@@ -20674,7 +20746,7 @@
         <v>58</v>
       </c>
       <c r="W63" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="X63" t="str">
         <v>South-West Scania, Sweden</v>
@@ -20688,7 +20760,7 @@
     </row>
     <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G64" t="str">
         <v>Generalized linear model</v>
@@ -20714,7 +20786,7 @@
     </row>
     <row r="65" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C65" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G65" t="str">
         <v>Generation logit model</v>
@@ -20740,7 +20812,7 @@
     </row>
     <row r="66" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C66" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G66" t="str">
         <v>Genetic Algorithm</v>
@@ -20758,7 +20830,7 @@
         <v>Suwon, South Korea</v>
       </c>
       <c r="AD66" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="AE66">
         <v>3</v>
@@ -20766,7 +20838,7 @@
     </row>
     <row r="67" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C67" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="G67" t="str">
         <v>Geo-conv Long Short-term Memory model</v>
@@ -20784,7 +20856,7 @@
         <v>Sydney, Australia</v>
       </c>
       <c r="AD67" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="AE67">
         <v>14</v>
@@ -20792,7 +20864,7 @@
     </row>
     <row r="68" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C68" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G68" t="str">
         <v>Gini</v>
@@ -20810,7 +20882,7 @@
         <v>Tainan, Taiwan</v>
       </c>
       <c r="AD68" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="AE68">
         <v>10</v>
@@ -20818,7 +20890,7 @@
     </row>
     <row r="69" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C69" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G69" t="str">
         <v>Gini-Indexes</v>
@@ -20844,7 +20916,7 @@
     </row>
     <row r="70" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C70" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G70" t="str">
         <v>GMM</v>
@@ -20853,10 +20925,10 @@
         <v>589</v>
       </c>
       <c r="Q70" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="W70" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="X70" t="str">
         <v>The Hague, Netherlands</v>
@@ -20870,7 +20942,7 @@
     </row>
     <row r="71" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C71" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="G71" t="str">
         <v>Gradient Boost decision tree</v>
@@ -20888,7 +20960,7 @@
         <v>Washington, DC, United States of America</v>
       </c>
       <c r="AD71" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AE71">
         <v>3</v>
@@ -20896,7 +20968,7 @@
     </row>
     <row r="72" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C72" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G72" t="str">
         <v>Gradient boosting</v>
@@ -20922,7 +20994,7 @@
     </row>
     <row r="73" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C73" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="G73" t="str">
         <v>Graph model</v>
@@ -20931,7 +21003,7 @@
         <v>58</v>
       </c>
       <c r="Q73" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="W73" t="s">
         <v>84</v>
@@ -20948,7 +21020,7 @@
     </row>
     <row r="74" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C74" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="G74" t="str">
         <v>Gravity-based model</v>
@@ -20966,7 +21038,7 @@
         <v>Wuhu, China</v>
       </c>
       <c r="AD74" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AE74">
         <v>7</v>
@@ -20974,7 +21046,7 @@
     </row>
     <row r="75" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C75" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="G75" t="str">
         <v>group mobility correlation</v>
@@ -21000,7 +21072,7 @@
     </row>
     <row r="76" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C76" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="G76" t="str">
         <v>GWNBR</v>
@@ -21041,7 +21113,7 @@
         <v>54</v>
       </c>
       <c r="AD77" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AE77">
         <v>0</v>
@@ -21055,7 +21127,7 @@
         <v>Hamming algorithm</v>
       </c>
       <c r="P78" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q78" t="s">
         <v>32</v>
@@ -21095,7 +21167,7 @@
     </row>
     <row r="80" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C80" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="G80" t="str">
         <v>Hidden Markov Model</v>
@@ -21118,7 +21190,7 @@
     </row>
     <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="G81" t="str">
         <v>Hierarchical mixture model</v>
@@ -21133,7 +21205,7 @@
         <v>485</v>
       </c>
       <c r="AD81" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="AE81">
         <v>15</v>
@@ -21141,7 +21213,7 @@
     </row>
     <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="G82" t="str">
         <v>HIERARCHICHAL AGGLOMERATIVE CLUSTERING</v>
@@ -21164,7 +21236,7 @@
     </row>
     <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="G83" t="str">
         <v>Historical average time series</v>
@@ -21173,7 +21245,7 @@
         <v>32</v>
       </c>
       <c r="Q83" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="W83" t="s">
         <v>54</v>
@@ -21187,7 +21259,7 @@
     </row>
     <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="G84" t="str">
         <v>ID-based dataset clustering</v>
@@ -21196,7 +21268,7 @@
         <v>79</v>
       </c>
       <c r="Q84" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="W84" t="s">
         <v>989</v>
@@ -21210,7 +21282,7 @@
     </row>
     <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="G85" t="str">
         <v>IDW interpolation</v>
@@ -21245,7 +21317,7 @@
         <v>510</v>
       </c>
       <c r="W86" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AD86" t="s">
         <v>499</v>
@@ -21256,7 +21328,7 @@
     </row>
     <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="G87" t="str">
         <v>Inner-PNN-AECM</v>
@@ -21271,7 +21343,7 @@
         <v>704</v>
       </c>
       <c r="AD87" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="AE87">
         <v>16</v>
@@ -21279,7 +21351,7 @@
     </row>
     <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="G88" t="str">
         <v>IS2Fun</v>
@@ -21288,13 +21360,13 @@
         <v>58</v>
       </c>
       <c r="Q88" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="W88" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AD88" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="AE88">
         <v>17</v>
@@ -21302,7 +21374,7 @@
     </row>
     <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="G89" t="str">
         <v>Jenks’ Natural Breaks</v>
@@ -21325,7 +21397,7 @@
     </row>
     <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G90" t="str">
         <v>Jensen-Shannon divergence</v>
@@ -21380,10 +21452,10 @@
         <v>736</v>
       </c>
       <c r="Q92" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="W92" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="AD92" t="s">
         <v>570</v>
@@ -21394,7 +21466,7 @@
     </row>
     <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G93" t="str">
         <v>k-NN</v>
@@ -21403,7 +21475,7 @@
         <v>46</v>
       </c>
       <c r="Q93" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="W93" t="s">
         <v>743</v>
@@ -21417,7 +21489,7 @@
     </row>
     <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G94" t="str">
         <v>Lagrange Multiplier</v>
@@ -21478,7 +21550,7 @@
         <v>183</v>
       </c>
       <c r="AD96" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="AE96">
         <v>0</v>
@@ -21486,7 +21558,7 @@
     </row>
     <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="G97" t="str">
         <v>Latent profile analysis clustering</v>
@@ -21509,7 +21581,7 @@
     </row>
     <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="G98" t="str">
         <v>Lattent Dirichlet Allocation</v>
@@ -21532,7 +21604,7 @@
     </row>
     <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="G99" t="str">
         <v>LDA</v>
@@ -21558,7 +21630,7 @@
     </row>
     <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="G100" t="str">
         <v>LGBM</v>
@@ -21581,7 +21653,7 @@
     </row>
     <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="G101" t="str">
         <v>LightGBM</v>
@@ -21604,7 +21676,7 @@
     </row>
     <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="G102" t="str">
         <v>Linear programming</v>
@@ -21613,7 +21685,7 @@
         <v>805</v>
       </c>
       <c r="Q102" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="W102" t="s">
         <v>84</v>
@@ -21627,7 +21699,7 @@
     </row>
     <row r="103" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C103" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G103" t="str">
         <v>linear regression</v>
@@ -21636,7 +21708,7 @@
         <v>373</v>
       </c>
       <c r="Q103" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="W103" t="s">
         <v>282</v>
@@ -21650,7 +21722,7 @@
     </row>
     <row r="104" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C104" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G104" t="str">
         <v>Local indicators of spatial association clustering</v>
@@ -21673,7 +21745,7 @@
     </row>
     <row r="105" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C105" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G105" t="str">
         <v>Local outlier factor</v>
@@ -21685,7 +21757,7 @@
         <v>58</v>
       </c>
       <c r="W105" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AD105" t="s">
         <v>685</v>
@@ -21696,7 +21768,7 @@
     </row>
     <row r="106" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C106" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G106" t="str">
         <v>logistic regresion</v>
@@ -21705,7 +21777,7 @@
         <v>46</v>
       </c>
       <c r="Q106" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="W106" t="s">
         <v>28</v>
@@ -21719,7 +21791,7 @@
     </row>
     <row r="107" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C107" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G107" t="str">
         <v>Logistic regression</v>
@@ -21742,7 +21814,7 @@
     </row>
     <row r="108" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C108" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="G108" t="str">
         <v>Logistic regression model</v>
@@ -21774,7 +21846,7 @@
         <v>373</v>
       </c>
       <c r="Q109" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="W109" t="s">
         <v>371</v>
@@ -21788,7 +21860,7 @@
     </row>
     <row r="110" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C110" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G110" t="str">
         <v>Long short-term memory</v>
@@ -21797,7 +21869,7 @@
         <v>510</v>
       </c>
       <c r="Q110" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="W110" t="s">
         <v>859</v>
@@ -21811,7 +21883,7 @@
     </row>
     <row r="111" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C111" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="G111" t="str">
         <v>Long-short term memory neural network</v>
@@ -21834,7 +21906,7 @@
     </row>
     <row r="112" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C112" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="G112" t="str">
         <v>Lorenz Curves</v>
@@ -21872,7 +21944,7 @@
         <v>127</v>
       </c>
       <c r="AD113" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="AE113">
         <v>3</v>
@@ -21886,7 +21958,7 @@
         <v>Markov chain Monte Carlo</v>
       </c>
       <c r="P114" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q114" t="s">
         <v>510</v>
@@ -21918,7 +21990,7 @@
         <v>326</v>
       </c>
       <c r="AD115" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="AE115">
         <v>7</v>
@@ -22001,13 +22073,13 @@
         <v>MLP</v>
       </c>
       <c r="P119" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q119" t="s">
         <v>30</v>
       </c>
       <c r="W119" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AD119" t="s">
         <v>868</v>
@@ -22018,7 +22090,7 @@
     </row>
     <row r="120" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C120" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G120" t="str">
         <v>Mobility pattern estimation: Clustering: k-means and hierarchical agglomerative</v>
@@ -22027,7 +22099,7 @@
         <v>30</v>
       </c>
       <c r="Q120" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="W120" t="s">
         <v>918</v>
@@ -22041,7 +22113,7 @@
     </row>
     <row r="121" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C121" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G121" t="str">
         <v>Modularity-based community detection algorithm</v>
@@ -22064,7 +22136,7 @@
     </row>
     <row r="122" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C122" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G122" t="str">
         <v>mPat Architecture</v>
@@ -22110,7 +22182,7 @@
     </row>
     <row r="124" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C124" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="G124" t="str">
         <v>Multinomial logit</v>
@@ -22125,7 +22197,7 @@
         <v>942</v>
       </c>
       <c r="AD124" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="AE124">
         <v>33</v>
@@ -22133,7 +22205,7 @@
     </row>
     <row r="125" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C125" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G125" t="str">
         <v>Multinomial logit model</v>
@@ -22171,7 +22243,7 @@
         <v>634</v>
       </c>
       <c r="AD126" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="AE126">
         <v>121</v>
@@ -22217,7 +22289,7 @@
         <v>752</v>
       </c>
       <c r="AD128" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="AE128">
         <v>16</v>
@@ -22225,7 +22297,7 @@
     </row>
     <row r="129" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C129" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G129" t="str">
         <v>Multi-task transfer passenger flow prediction</v>
@@ -22248,7 +22320,7 @@
     </row>
     <row r="130" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C130" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G130" t="str">
         <v>multivariable regression model</v>
@@ -22260,7 +22332,7 @@
         <v>193</v>
       </c>
       <c r="W130" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AD130" t="s">
         <v>697</v>
@@ -22271,7 +22343,7 @@
     </row>
     <row r="131" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C131" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G131" t="str">
         <v>Multivariate ordinary least square regression</v>
@@ -22294,7 +22366,7 @@
     </row>
     <row r="132" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C132" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="G132" t="str">
         <v>Multivariate regression model</v>
@@ -22340,7 +22412,7 @@
     </row>
     <row r="134" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C134" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="G134" t="str">
         <v>Naïve Bayes</v>
@@ -22355,7 +22427,7 @@
         <v>485</v>
       </c>
       <c r="AD134" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="AE134">
         <v>63</v>
@@ -22363,7 +22435,7 @@
     </row>
     <row r="135" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C135" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G135" t="str">
         <v>NARX</v>
@@ -22386,7 +22458,7 @@
     </row>
     <row r="136" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C136" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="G136" t="str">
         <v>Negative binomial regression</v>
@@ -22409,7 +22481,7 @@
     </row>
     <row r="137" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C137" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="G137" t="str">
         <v>Neural network</v>
@@ -22432,7 +22504,7 @@
     </row>
     <row r="138" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C138" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G138" t="str">
         <v>n-gram</v>
@@ -22470,7 +22542,7 @@
         <v>1028</v>
       </c>
       <c r="AD139" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AE139">
         <v>90</v>
@@ -22507,16 +22579,16 @@
         <v>non-negative tensor factorization</v>
       </c>
       <c r="P141" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q141" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="W141" t="s">
         <v>54</v>
       </c>
       <c r="AD141" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="AE141">
         <v>219</v>
@@ -22524,7 +22596,7 @@
     </row>
     <row r="142" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C142" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="G142" t="str">
         <v>Normalized Mutual Information</v>
@@ -22547,7 +22619,7 @@
     </row>
     <row r="143" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C143" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="G143" t="str">
         <v>OD analysis</v>
@@ -22570,13 +22642,13 @@
     </row>
     <row r="144" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C144" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="G144" t="str">
         <v>OD matrix</v>
       </c>
       <c r="P144" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="Q144" t="s">
         <v>574</v>
@@ -22593,19 +22665,19 @@
     </row>
     <row r="145" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C145" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="G145" t="str">
         <v>ODX</v>
       </c>
       <c r="P145" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q145" t="s">
         <v>58</v>
       </c>
       <c r="W145" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="AD145" t="s">
         <v>840</v>
@@ -22616,19 +22688,19 @@
     </row>
     <row r="146" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C146" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G146" t="str">
         <v>OLS</v>
       </c>
       <c r="P146" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q146" t="s">
         <v>58</v>
       </c>
       <c r="W146" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="AD146" t="s">
         <v>933</v>
@@ -22639,19 +22711,19 @@
     </row>
     <row r="147" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C147" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="G147" t="str">
         <v>Ordinary least squares</v>
       </c>
       <c r="P147" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q147" t="s">
         <v>32</v>
       </c>
       <c r="W147" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="AD147" t="s">
         <v>975</v>
@@ -22668,7 +22740,7 @@
         <v>Ordinary least squares regresssion</v>
       </c>
       <c r="P148" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q148" t="s">
         <v>30</v>
@@ -22685,22 +22757,22 @@
     </row>
     <row r="149" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C149" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="G149" t="str">
         <v>Ortegatong et al. 2013</v>
       </c>
       <c r="P149" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="Q149" t="s">
         <v>58</v>
       </c>
       <c r="W149" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="AD149" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="AE149">
         <v>22</v>
@@ -22708,7 +22780,7 @@
     </row>
     <row r="150" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C150" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G150" t="str">
         <v>PageRank</v>
@@ -22717,10 +22789,10 @@
         <v>984</v>
       </c>
       <c r="Q150" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="W150" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="AD150" t="s">
         <v>980</v>
@@ -22737,13 +22809,13 @@
         <v>Panel data model</v>
       </c>
       <c r="P151" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="Q151" t="s">
         <v>481</v>
       </c>
       <c r="W151" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="AD151" t="s">
         <v>891</v>
@@ -22760,7 +22832,7 @@
         <v>Partitioning around medoids</v>
       </c>
       <c r="P152" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="Q152" t="s">
         <v>728</v>
@@ -22777,19 +22849,19 @@
     </row>
     <row r="153" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C153" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="G153" t="str">
         <v>passenger arrival rate prediction model</v>
       </c>
       <c r="P153" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="Q153" t="s">
         <v>58</v>
       </c>
       <c r="W153" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="AD153" t="s">
         <v>795</v>
@@ -22800,7 +22872,7 @@
     </row>
     <row r="154" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C154" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="G154" t="str">
         <v>Passenger profiling algorithm</v>
@@ -22812,7 +22884,7 @@
         <v>58</v>
       </c>
       <c r="W154" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="AD154" t="s">
         <v>910</v>
@@ -22829,7 +22901,7 @@
         <v>Passenger to train assignment</v>
       </c>
       <c r="P155" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q155" t="s">
         <v>32</v>
@@ -22858,7 +22930,7 @@
         <v>32</v>
       </c>
       <c r="W156" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AD156" t="s">
         <v>902</v>
@@ -22869,22 +22941,22 @@
     </row>
     <row r="157" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C157" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="G157" t="str">
         <v>PCA</v>
       </c>
       <c r="P157" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="Q157" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="W157" t="s">
         <v>84</v>
       </c>
       <c r="AD157" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="AE157">
         <v>12</v>
@@ -22892,19 +22964,19 @@
     </row>
     <row r="158" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C158" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="G158" t="str">
         <v>P-DN</v>
       </c>
       <c r="P158" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="Q158" t="s">
         <v>193</v>
       </c>
       <c r="W158" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="AD158" t="s">
         <v>803</v>
@@ -22915,7 +22987,7 @@
     </row>
     <row r="159" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C159" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="G159" t="str">
         <v>Poisson distribution</v>
@@ -22927,7 +22999,7 @@
         <v>32</v>
       </c>
       <c r="W159" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="AD159" t="s">
         <v>681</v>
@@ -22938,19 +23010,19 @@
     </row>
     <row r="160" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C160" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="G160" t="str">
         <v>Poisson mixture</v>
       </c>
       <c r="P160" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="Q160" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="W160" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="AD160" t="s">
         <v>791</v>
@@ -22961,13 +23033,13 @@
     </row>
     <row r="161" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C161" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="G161" t="str">
         <v>Probabilistic model</v>
       </c>
       <c r="P161" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="Q161" t="s">
         <v>32</v>
@@ -22990,7 +23062,7 @@
         <v>Probability distribution functions</v>
       </c>
       <c r="P162" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="Q162" t="s">
         <v>79</v>
@@ -23013,7 +23085,7 @@
         <v>Probability model</v>
       </c>
       <c r="P163" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="Q163" t="s">
         <v>481</v>
@@ -23042,7 +23114,7 @@
         <v>193</v>
       </c>
       <c r="W164" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="AD164" t="s">
         <v>1015</v>
@@ -23059,13 +23131,13 @@
         <v>Product-based spatial and temporal module with Inner-product neural network + Auto-encoder-based compression module</v>
       </c>
       <c r="P165" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="Q165" t="s">
         <v>32</v>
       </c>
       <c r="W165" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="AD165" t="s">
         <v>873</v>
@@ -23076,7 +23148,7 @@
     </row>
     <row r="166" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C166" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="G166" t="str">
         <v>PSTM</v>
@@ -23099,13 +23171,13 @@
     </row>
     <row r="167" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C167" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="G167" t="str">
         <v>Random forest</v>
       </c>
       <c r="P167" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q167" t="s">
         <v>58</v>
@@ -23128,7 +23200,7 @@
         <v>Random Utility Maximization</v>
       </c>
       <c r="P168" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q168" t="s">
         <v>46</v>
@@ -23151,7 +23223,7 @@
         <v>Random Utility Model</v>
       </c>
       <c r="P169" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q169" t="s">
         <v>32</v>
@@ -23168,7 +23240,7 @@
     </row>
     <row r="170" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C170" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="G170" t="str">
         <v>Ranking Algorithm</v>
@@ -23180,10 +23252,10 @@
         <v>32</v>
       </c>
       <c r="W170" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AD170" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="AE170">
         <v>27</v>
@@ -23197,7 +23269,7 @@
         <v>Recurrent neural networks</v>
       </c>
       <c r="P171" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q171" t="s">
         <v>32</v>
@@ -23214,22 +23286,22 @@
     </row>
     <row r="172" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C172" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G172" t="str">
         <v>regression analysis</v>
       </c>
       <c r="P172" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q172" t="s">
         <v>32</v>
       </c>
       <c r="W172" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="AD172" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="AE172">
         <v>128</v>
@@ -23243,7 +23315,7 @@
         <v>regression model</v>
       </c>
       <c r="P173" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q173" t="s">
         <v>728</v>
@@ -23269,7 +23341,7 @@
         <v>481</v>
       </c>
       <c r="Q174" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="W174" t="s">
         <v>54</v>
@@ -23283,7 +23355,7 @@
     </row>
     <row r="175" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C175" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G175" t="str">
         <v>Reliability Buffer Time</v>
@@ -23295,10 +23367,10 @@
         <v>32</v>
       </c>
       <c r="W175" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="AD175" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="AE175">
         <v>10</v>
@@ -23306,7 +23378,7 @@
     </row>
     <row r="176" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C176" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="G176" t="str">
         <v>ReliefF</v>
@@ -23318,7 +23390,7 @@
         <v>58</v>
       </c>
       <c r="W176" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="AD176" t="s">
         <v>827</v>
@@ -23341,7 +23413,7 @@
         <v>46</v>
       </c>
       <c r="W177" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="178" spans="3:23" x14ac:dyDescent="0.2">
@@ -23352,7 +23424,7 @@
         <v>RNN</v>
       </c>
       <c r="P178" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q178" t="s">
         <v>58</v>
@@ -23360,7 +23432,7 @@
     </row>
     <row r="179" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C179" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G179" t="str">
         <v>Rodriguez–Laio 2014</v>
@@ -23371,7 +23443,7 @@
     </row>
     <row r="180" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C180" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G180" t="str">
         <v>Route travel time prediction model</v>
@@ -23382,7 +23454,7 @@
     </row>
     <row r="181" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C181" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G181" t="str">
         <v>Route-based analysis</v>
@@ -23393,7 +23465,7 @@
     </row>
     <row r="182" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C182" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G182" t="str">
         <v>rule-based procedure</v>
@@ -23426,7 +23498,7 @@
     </row>
     <row r="185" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C185" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G185" t="str">
         <v>SHAP</v>
@@ -23437,7 +23509,7 @@
     </row>
     <row r="186" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C186" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="G186" t="str">
         <v>Shapley Additive Explanations</v>
@@ -23448,7 +23520,7 @@
     </row>
     <row r="187" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C187" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="G187" t="str">
         <v>Single-layer perceptron neural networks</v>
@@ -23459,7 +23531,7 @@
     </row>
     <row r="188" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C188" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G188" t="str">
         <v>SMOTE</v>
@@ -23503,7 +23575,7 @@
     </row>
     <row r="192" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C192" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="G192" t="str">
         <v>Spatial Error Model</v>
@@ -23514,7 +23586,7 @@
     </row>
     <row r="193" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C193" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G193" t="str">
         <v>Spatial lag</v>
@@ -23525,7 +23597,7 @@
     </row>
     <row r="194" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C194" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="G194" t="str">
         <v>Spatial lag model</v>
@@ -23536,7 +23608,7 @@
     </row>
     <row r="195" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C195" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="G195" t="str">
         <v>Spatial log model</v>
@@ -23547,7 +23619,7 @@
     </row>
     <row r="196" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C196" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="G196" t="str">
         <v>Spectral Clustering</v>
@@ -23558,7 +23630,7 @@
     </row>
     <row r="197" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C197" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G197" t="str">
         <v>STGGA</v>
@@ -23580,7 +23652,7 @@
     </row>
     <row r="199" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C199" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G199" t="str">
         <v>Stochastic modeling</v>
@@ -23690,7 +23762,7 @@
     </row>
     <row r="209" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C209" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="G209" t="str">
         <v>time series analysis</v>
@@ -23701,7 +23773,7 @@
     </row>
     <row r="210" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C210" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G210" t="str">
         <v>top-k neighbor</v>
@@ -23712,7 +23784,7 @@
     </row>
     <row r="211" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C211" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="G211" t="str">
         <v>Transit competitiveness index</v>
@@ -23723,18 +23795,18 @@
     </row>
     <row r="212" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C212" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G212" t="str">
         <v>Transit tensor factorization</v>
       </c>
       <c r="Q212" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="213" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C213" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G213" t="str">
         <v>trip choice model</v>
@@ -23756,7 +23828,7 @@
     </row>
     <row r="215" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C215" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="G215" t="str">
         <v>trip reconstruction</v>
@@ -23767,7 +23839,7 @@
     </row>
     <row r="216" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C216" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G216" t="str">
         <v>trip-chaining</v>
@@ -23789,7 +23861,7 @@
     </row>
     <row r="218" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C218" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="G218" t="str">
         <v>Unidirectional Long short-term memory</v>
@@ -23800,7 +23872,7 @@
     </row>
     <row r="219" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C219" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="G219" t="str">
         <v>Vector space model</v>
@@ -23811,7 +23883,7 @@
     </row>
     <row r="220" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C220" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G220" t="str">
         <v>Ward's algorithm</v>
@@ -23828,12 +23900,12 @@
         <v>WS-DBSCAN</v>
       </c>
       <c r="Q221" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="222" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C222" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="G222" t="str">
         <v>XGB</v>
@@ -23877,7 +23949,7 @@
     </row>
     <row r="226" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C226" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="Q226" t="s">
         <v>32</v>
@@ -23885,7 +23957,7 @@
     </row>
     <row r="227" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C227" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="Q227" t="s">
         <v>58</v>
@@ -23920,12 +23992,12 @@
         <v>955</v>
       </c>
       <c r="Q231" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="232" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C232" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="Q232" t="s">
         <v>79</v>
@@ -23965,7 +24037,7 @@
     </row>
     <row r="237" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C237" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="Q237" t="s">
         <v>58</v>
@@ -23973,7 +24045,7 @@
     </row>
     <row r="238" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C238" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="Q238" t="s">
         <v>32</v>
@@ -24000,12 +24072,12 @@
         <v>321</v>
       </c>
       <c r="Q241" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="242" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C242" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q242" t="s">
         <v>58</v>
@@ -24013,7 +24085,7 @@
     </row>
     <row r="243" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C243" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q243" t="s">
         <v>32</v>
@@ -24037,7 +24109,7 @@
     </row>
     <row r="246" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C246" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q246" t="s">
         <v>193</v>
@@ -24045,7 +24117,7 @@
     </row>
     <row r="247" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C247" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q247" t="s">
         <v>193</v>
@@ -24053,7 +24125,7 @@
     </row>
     <row r="248" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C248" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q248" t="s">
         <v>58</v>
@@ -24069,7 +24141,7 @@
     </row>
     <row r="250" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C250" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q250" t="s">
         <v>58</v>
@@ -24077,7 +24149,7 @@
     </row>
     <row r="251" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C251" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q251" t="s">
         <v>58</v>
@@ -24085,7 +24157,7 @@
     </row>
     <row r="252" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C252" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q252" t="s">
         <v>58</v>
@@ -24093,7 +24165,7 @@
     </row>
     <row r="253" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C253" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q253" t="s">
         <v>58</v>
@@ -24101,34 +24173,34 @@
     </row>
     <row r="254" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C254" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q254" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="255" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C255" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="Q255" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="256" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C256" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q256" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="257" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C257" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q257" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="258" spans="3:17" x14ac:dyDescent="0.2">
@@ -24160,12 +24232,12 @@
         <v>204</v>
       </c>
       <c r="Q261" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="262" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C262" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q262" t="s">
         <v>30</v>
@@ -24173,7 +24245,7 @@
     </row>
     <row r="263" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C263" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q263" t="s">
         <v>30</v>
@@ -24189,7 +24261,7 @@
     </row>
     <row r="265" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C265" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q265" t="s">
         <v>30</v>
@@ -24197,7 +24269,7 @@
     </row>
     <row r="266" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C266" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="Q266" t="s">
         <v>30</v>
@@ -24205,15 +24277,15 @@
     </row>
     <row r="267" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C267" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="Q267" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="268" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C268" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="Q268" t="s">
         <v>32</v>
@@ -24229,15 +24301,15 @@
     </row>
     <row r="270" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C270" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="Q270" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="271" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C271" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q271" t="s">
         <v>30</v>
@@ -24245,7 +24317,7 @@
     </row>
     <row r="272" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C272" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="Q272" t="s">
         <v>32</v>
@@ -24261,10 +24333,10 @@
     </row>
     <row r="274" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C274" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q274" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="275" spans="3:17" x14ac:dyDescent="0.2">
@@ -24272,28 +24344,28 @@
         <v>336</v>
       </c>
       <c r="Q275" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="276" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C276" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="Q276" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="277" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C277" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="Q277" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="278" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C278" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="Q278" t="s">
         <v>58</v>
@@ -24301,7 +24373,7 @@
     </row>
     <row r="279" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C279" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="Q279" t="s">
         <v>46</v>
@@ -24317,7 +24389,7 @@
     </row>
     <row r="281" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C281" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="Q281" t="s">
         <v>984</v>
@@ -24325,7 +24397,7 @@
     </row>
     <row r="282" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C282" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="Q282" t="s">
         <v>58</v>
@@ -24333,7 +24405,7 @@
     </row>
     <row r="283" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C283" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="Q283" t="s">
         <v>728</v>
@@ -24341,7 +24413,7 @@
     </row>
     <row r="284" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C284" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="Q284" t="s">
         <v>481</v>
@@ -24349,15 +24421,15 @@
     </row>
     <row r="285" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C285" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="Q285" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="286" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C286" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q286" t="s">
         <v>32</v>
@@ -24365,7 +24437,7 @@
     </row>
     <row r="287" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C287" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q287" t="s">
         <v>193</v>
@@ -24373,7 +24445,7 @@
     </row>
     <row r="288" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C288" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q288" t="s">
         <v>46</v>
@@ -24392,7 +24464,7 @@
         <v>204</v>
       </c>
       <c r="Q290" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="291" spans="3:17" x14ac:dyDescent="0.2">
@@ -24413,15 +24485,15 @@
     </row>
     <row r="293" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C293" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q293" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="294" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C294" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q294" t="s">
         <v>32</v>
@@ -24437,7 +24509,7 @@
     </row>
     <row r="296" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C296" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q296" t="s">
         <v>32</v>
@@ -24453,7 +24525,7 @@
     </row>
     <row r="298" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C298" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q298" t="s">
         <v>984</v>
@@ -24461,7 +24533,7 @@
     </row>
     <row r="299" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C299" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="Q299" t="s">
         <v>984</v>
@@ -24469,15 +24541,15 @@
     </row>
     <row r="300" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C300" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q300" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="301" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C301" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q301" t="s">
         <v>58</v>
@@ -24485,7 +24557,7 @@
     </row>
     <row r="302" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C302" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="Q302" t="s">
         <v>30</v>
@@ -24493,7 +24565,7 @@
     </row>
     <row r="303" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C303" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q303" t="s">
         <v>46</v>
@@ -24504,12 +24576,12 @@
         <v>46</v>
       </c>
       <c r="Q304" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="305" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C305" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q305" t="s">
         <v>79</v>
@@ -24525,7 +24597,7 @@
     </row>
     <row r="307" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C307" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q307" t="s">
         <v>46</v>
@@ -24536,7 +24608,7 @@
         <v>46</v>
       </c>
       <c r="Q308" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="309" spans="3:17" x14ac:dyDescent="0.2">
@@ -24576,12 +24648,12 @@
         <v>79</v>
       </c>
       <c r="Q313" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="314" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C314" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q314" t="s">
         <v>728</v>
@@ -24589,15 +24661,15 @@
     </row>
     <row r="315" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C315" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q315" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="316" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C316" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q316" t="s">
         <v>58</v>
@@ -24605,7 +24677,7 @@
     </row>
     <row r="317" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C317" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q317" t="s">
         <v>58</v>
@@ -24613,7 +24685,7 @@
     </row>
     <row r="318" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C318" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="Q318" t="s">
         <v>618</v>
@@ -24621,7 +24693,7 @@
     </row>
     <row r="319" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C319" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="Q319" t="s">
         <v>30</v>
@@ -24629,7 +24701,7 @@
     </row>
     <row r="320" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C320" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="Q320" t="s">
         <v>30</v>
@@ -24637,7 +24709,7 @@
     </row>
     <row r="321" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C321" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="Q321" t="s">
         <v>30</v>
@@ -24645,7 +24717,7 @@
     </row>
     <row r="322" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C322" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Q322" t="s">
         <v>618</v>
@@ -24653,7 +24725,7 @@
     </row>
     <row r="323" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C323" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="Q323" t="s">
         <v>32</v>
@@ -24701,7 +24773,7 @@
     </row>
     <row r="329" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C329" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="Q329" t="s">
         <v>30</v>
@@ -24709,7 +24781,7 @@
     </row>
     <row r="330" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C330" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="Q330" t="s">
         <v>58</v>
@@ -24717,7 +24789,7 @@
     </row>
     <row r="331" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C331" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q331" t="s">
         <v>510</v>
@@ -24725,15 +24797,15 @@
     </row>
     <row r="332" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C332" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q332" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="333" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C333" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="Q333" t="s">
         <v>193</v>
@@ -24741,7 +24813,7 @@
     </row>
     <row r="334" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C334" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="Q334" t="s">
         <v>193</v>
@@ -24749,7 +24821,7 @@
     </row>
     <row r="335" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C335" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
   </sheetData>
